--- a/data/trans_orig/IP07C10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10693</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21446</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14030</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>24268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26275</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42200</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,17%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14591</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>26430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>57,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23788</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38813</t>
+          <t>38257</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5607</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14861</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,16%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3564</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64502</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85092</t>
+          <t>85408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69917</t>
+          <t>70246</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92780</t>
+          <t>92330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139163</t>
+          <t>139058</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170401</t>
+          <t>170949</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72117</t>
+          <t>71722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94332</t>
+          <t>93372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>80453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103073</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159235</t>
+          <t>158179</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190800</t>
+          <t>191959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,6%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35394</t>
+          <t>35507</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49784</t>
+          <t>49786</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56427</t>
+          <t>57568</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80825</t>
+          <t>81525</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23772</t>
+          <t>24864</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>22489</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27414</t>
+          <t>27835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42739</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>16838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28919</t>
+          <t>28231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>26625</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35620</t>
+          <t>34947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>51,02%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15768</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12173</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25118</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>95089</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>121379</t>
+          <t>121488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104230</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>130986</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245515</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>112991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>109087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>228288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>267085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>123741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10651</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>19522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>22499</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>36820</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>18293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29623</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35085</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51141</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>3550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12738</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12227</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54156</t>
+          <t>53032</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74861</t>
+          <t>75588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79809</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103328</t>
+          <t>102821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139930</t>
+          <t>139284</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>173243</t>
+          <t>171223</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82507</t>
+          <t>83333</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105519</t>
+          <t>105119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84086</t>
+          <t>84821</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108438</t>
+          <t>107427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172495</t>
+          <t>173034</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207714</t>
+          <t>207207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23086</t>
+          <t>23040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39977</t>
+          <t>39706</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30998</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>43751</t>
+          <t>42916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65078</t>
+          <t>65059</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10830</t>
+          <t>10498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19669</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32061</t>
+          <t>32322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51014</t>
+          <t>52028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32164</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>22971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34553</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>43706</t>
+          <t>44944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62570</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,51%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>13404</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10555</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22842</t>
+          <t>22721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119529</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>107868</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136017</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>208006</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248685</t>
+          <t>246483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>128681</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>156157</t>
+          <t>156781</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>129275</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>158250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266985</t>
+          <t>265068</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306529</t>
+          <t>306428</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16157</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>28762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,6%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13441</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22629</t>
+          <t>22687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25983</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,94%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -6994,7 +6994,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91516</t>
+          <t>92198</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117544</t>
+          <t>117360</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78610</t>
+          <t>78313</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103421</t>
+          <t>103917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178200</t>
+          <t>179179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214082</t>
+          <t>212393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>82779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107841</t>
+          <t>107403</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91513</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116645</t>
+          <t>115373</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182527</t>
+          <t>182340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218091</t>
+          <t>220043</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22133</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>40695</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>39162</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49450</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73835</t>
+          <t>72436</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,82 +7686,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1302</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8576</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>6160</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>11439</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>2,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3763</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1319</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7982</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>6160</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3207</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>11295</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18656</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29059</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>43053</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50380</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>70791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25447</t>
+          <t>25304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39593</t>
+          <t>38934</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36678</t>
+          <t>37619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>51655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72209</t>
+          <t>71151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18640</t>
+          <t>18481</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -8393,7 +8393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3574</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125441</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>155944</t>
+          <t>156022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259339</t>
+          <t>257749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>300514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127944</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>157467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>165913</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>315800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>107927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/IP07C10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19166</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13951</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24576</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>45,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,26%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>58,59%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10052</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20878</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10762</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21083</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,99%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>45,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>19166</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13803</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24268</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>45,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>28146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42375</t>
+          <t>42578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,41%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10712</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15390</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25,54%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>36,69%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20353</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>15335</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26430</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14353</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25476</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>57,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10712</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>7045</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15646</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38257</t>
+          <t>38972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>11427</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16409</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>27,24%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39,12%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>9309</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5355</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14385</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5649</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14339</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>20,23%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>11,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>11427</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>7235</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16525</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>27,24%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>27657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -1061,107 +1061,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3786</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3271</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3564</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3548</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>7,71%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3361</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3288</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41947</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41947</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41947</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>46014</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41947</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41947</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80964</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70764</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>93678</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>43,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>74424</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>63469</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85408</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>64330</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>84950</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>80964</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>70246</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>92330</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139058</t>
+          <t>140609</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170949</t>
+          <t>172861</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>91797</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80223</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103367</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>37,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>47,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82815</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71722</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93372</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72361</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94012</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>44,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,29%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>91797</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>80453</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>102479</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>42,5%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158179</t>
+          <t>157823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>191959</t>
+          <t>190217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40604</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>31962</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,8%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,37%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>27410</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>35507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>20618</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>36102</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>14,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40604</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>31290</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>49786</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>55547</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81525</t>
+          <t>81188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1743,72 +1743,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5911</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2646</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6648</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6358</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,41%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5579</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2726</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>578</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2901</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2755</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>215972</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>215972</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>215972</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>187295</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>187295</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>187295</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>215972</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>215972</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>215972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17092</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12148</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23487</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>47,89%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18425</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13140</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24864</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12591</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24431</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>24,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17092</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11792</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22489</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>34,85%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27835</t>
+          <t>28373</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44694</t>
+          <t>43317</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -2204,67 +2204,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>20991</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>15890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>26934</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>22361</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>16838</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28231</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>29005</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>42,2%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>20991</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>15298</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>26625</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34947</t>
+          <t>36264</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,69%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7602</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4184</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12423</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>10737</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6215</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>15870</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>6297</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>16601</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>20,26%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4121</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>12439</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,5%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12679</t>
+          <t>12953</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -2425,92 +2425,92 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3355</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,74%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>3355</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1278</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>6,84%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2538,107 +2538,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1467</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4465</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4453</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,77%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>8,4%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1467</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5118</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>49040</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>52990</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>52990</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>52990</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>49040</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>117222</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>103981</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>131012</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33,87%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>42,68%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>108491</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>95716</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>121488</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>95594</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>121574</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>37,89%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>42,43%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>117222</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>103230</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>130986</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,19%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>206096</t>
+          <t>208505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>245856</t>
+          <t>248169</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -2881,74 +2881,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>123500</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>109865</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>138064</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>40,23%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35,79%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>125529</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>112991</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>139275</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>112960</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>139274</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>43,85%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>39,46%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>48,65%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>123500</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>109087</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>137752</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>40,23%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>35,54%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>371</t>
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>228288</t>
+          <t>229092</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>267085</t>
+          <t>267831</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>59632</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>48800</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>71870</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>19,43%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>15,9%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>47457</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>38544</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>57987</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>37609</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>58096</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>16,58%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>20,25%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>59632</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>49995</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>71559</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>19,43%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>92263</t>
+          <t>92313</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>123741</t>
+          <t>122867</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6026</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3242</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10601</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>2646</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6977</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6026</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10814</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -3220,72 +3220,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>578</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3464</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6498</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5831</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>306959</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>425</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>286300</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>286300</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>286300</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>306959</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13478</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8906</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18686</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>16022</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10777</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21325</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11011</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21877</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>33,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13478</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8771</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19522</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22499</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36820</t>
+          <t>37080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19126</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13260</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>24645</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23526</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18293</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29426</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17476</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29508</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>49,6%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19126</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13654</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>25031</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>34248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49847</t>
+          <t>50289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10699</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15529</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,37%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>35,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7291</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3550</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3842</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11722</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>15,37%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10699</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6626</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15900</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>25291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -4020,107 +4020,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3554</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2918</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3082</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4133,107 +4133,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2992</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3018</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3009</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43910</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43910</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43910</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>47434</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>47434</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>47434</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43910</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43910</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>91164</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79008</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>104805</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>64280</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53032</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75588</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>53871</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>75201</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>33,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>91164</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>79354</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>102821</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139284</t>
+          <t>139802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171223</t>
+          <t>172681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>42,56%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>96565</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>84341</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>109348</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,07%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,66%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>94009</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>83333</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105119</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83243</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105397</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>49,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>43,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>55,38%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>96565</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>84821</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>107427</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>44,73%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173034</t>
+          <t>173641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207207</t>
+          <t>207332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,11%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22629</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15747</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30467</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>10,48%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>14,11%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>30769</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23040</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39706</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22379</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39230</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>16,21%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22629</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16103</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>29922</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>10,48%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>42916</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>65993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5508</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2617</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10514</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3869</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5508</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2680</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11259</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>215866</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>215866</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>215866</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>189826</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>189826</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>189826</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>215866</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>215866</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>215866</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17055</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11595</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23037</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>21,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>42,46%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25496</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19669</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>32322</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18269</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31547</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17055</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11815</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>22650</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>34114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52028</t>
+          <t>50668</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>28685</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23040</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35262</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42,47%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>65,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>24895</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>18521</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>31111</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>19151</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>31561</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,37%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>32,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>28685</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22971</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>34355</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>52,87%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>44944</t>
+          <t>44578</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>63201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>8512</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13546</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15,69%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>24,97%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>7011</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3421</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12578</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>11935</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>12,21%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>21,91%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>8512</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>4938</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13404</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>9866</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22721</t>
+          <t>22070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -5615,52 +5615,52 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>54253</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>54253</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>54253</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>57403</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>57403</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>57403</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>54253</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>54253</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>54253</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,107 +5727,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>121697</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>107298</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>135608</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,75%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>43,18%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>105799</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>92933</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>119254</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>93089</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>119242</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>35,9%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,54%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>31,59%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>40,47%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>121697</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>107868</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>136365</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,75%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>227495</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>209109</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>246368</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>37,37%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>34,35%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>227495</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>208006</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>246483</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>37,37%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>34,17%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144376</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>131511</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>160033</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,98%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>41,88%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>50,96%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>142431</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>129014</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>156781</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>128311</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>155414</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>48,34%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>43,78%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>53,21%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144376</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>129275</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>158250</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>45,98%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>265068</t>
+          <t>266801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>306428</t>
+          <t>306855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>41840</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>32602</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>52334</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>45071</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>35406</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>55677</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>35575</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>55516</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>15,3%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,02%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>41840</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>32799</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>52502</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73664</t>
+          <t>73825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>101649</t>
+          <t>101053</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11255</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3848</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4272</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6115</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3140</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>11061</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6179,92 +6179,92 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2980</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2997</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>314028</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>420</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>294663</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>294663</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>294663</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>314028</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres, percibida por el/la menor en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14029</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9673</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>19165</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>38,98%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>53,26%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8131</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4781</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12503</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12542</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,11%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,94%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14029</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9874</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19394</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>38,98%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>28586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,33%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17876</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12868</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22659</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>49,68%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,76%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>62,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15106</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10562</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19683</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10675</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19442</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>50,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>35,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17876</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13441</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22687</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>40077</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,75%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7045</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>5429</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2735</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>9859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2554</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9438</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>18,1%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>32,88%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3518</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7085</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14429</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -6984,102 +6984,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>706</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2715</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4056</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4176</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -7092,107 +7092,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3149</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3876</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>12,92%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3471</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>35985</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>35985</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>35985</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>29989</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>29989</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>29989</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>35985</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>35985</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>35985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90965</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>79383</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>102637</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>39,52%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>44,59%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>104732</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92198</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>117360</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>92380</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>117996</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>44,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90965</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>78313</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>103917</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>179179</t>
+          <t>178251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>212393</t>
+          <t>213549</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>103843</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89962</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>115954</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,08%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>95576</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82779</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>107403</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>84453</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>109936</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>40,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,96%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>103843</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>90751</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>115373</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>45,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>181868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>220043</t>
+          <t>216423</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>29821</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>22721</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>38691</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>16,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>31171</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>23904</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>40695</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>22552</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39546</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>13,17%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>29821</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>22524</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39162</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48297</t>
+          <t>49474</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>74527</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -7661,72 +7661,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3763</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8709</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2397</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5426</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3763</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1302</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8576</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5783</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2882</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7062</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7018</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,27%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5788</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9409</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>230178</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>230178</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>230178</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>236758</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>236758</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>236758</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>230178</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>230178</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>230178</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>35780</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42858</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>56,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25352</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18752</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31896</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19297</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>33234</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>36,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>45,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>35780</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42934</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,39%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>70791</t>
+          <t>71525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29202</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22360</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>36686</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>29,62%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>32345</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25304</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>38934</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25327</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>39762</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>46,3%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29202</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>22486</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>37619</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>38,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>51466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71151</t>
+          <t>71841</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,42%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9812</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5627</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>15872</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,45%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>21,02%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>12158</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7454</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18481</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7816</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>17975</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>17,4%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>26,46%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>9812</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>5443</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>15407</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>15864</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3639</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>708</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>4232</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3687</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>75502</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>69856</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>69856</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>69856</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>75502</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>140774</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>125856</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>155319</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>41,2%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>36,84%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>45,46%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>138215</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>122974</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>152817</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>123007</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>153030</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>41,06%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>45,4%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>140774</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>126821</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>156022</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>41,2%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>257749</t>
+          <t>256172</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>300514</t>
+          <t>300274</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>150921</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>135895</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>166577</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>44,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>48,75%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>143028</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>128777</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>157467</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>127013</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>157645</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>42,49%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,78%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>150921</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>134131</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>164874</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274137</t>
+          <t>272926</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>315800</t>
+          <t>317012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>43150</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>33587</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>53515</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>9,83%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>48758</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>37989</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>60132</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>38762</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>60910</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>14,49%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>17,86%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>43150</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>33792</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>53993</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>78304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107927</t>
+          <t>107101</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5034</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10479</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3103</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6457</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7165</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5034</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10491</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>13953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5773</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>3499</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7705</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1256</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7859</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1785</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6227</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2248</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>341665</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>479</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>336602</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>336602</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>336602</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>341665</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
